--- a/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
+++ b/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t>Record</t>
   </si>
@@ -30,19 +30,31 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Sacks and the City</t>
+  </si>
+  <si>
+    <t>It's Miller Time</t>
+  </si>
+  <si>
+    <t>Flock Around and Find Out</t>
+  </si>
+  <si>
     <t>Tush Push Director 🍑</t>
   </si>
   <si>
-    <t>Sacks and the City</t>
+    <t>Rolling with the Homies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurts so Good </t>
+  </si>
+  <si>
+    <t>Hurts Locker Room Talk</t>
   </si>
   <si>
     <t>Gridiron Grace</t>
   </si>
   <si>
-    <t xml:space="preserve">Hurts so Good </t>
-  </si>
-  <si>
-    <t>Hurts Locker Room Talk</t>
+    <t>Immaculate Concepcion</t>
   </si>
   <si>
     <t>Say Cheese 🧀💚🧀</t>
@@ -51,223 +63,166 @@
     <t>Third Down and Long Story</t>
   </si>
   <si>
-    <t>It's Miller Time</t>
-  </si>
-  <si>
-    <t>Bianca</t>
-  </si>
-  <si>
-    <t>Flock Around and Find Out</t>
-  </si>
-  <si>
-    <t>Immaculate Concepcion</t>
-  </si>
-  <si>
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>87.0%</t>
-  </si>
-  <si>
-    <t>83.8%</t>
-  </si>
-  <si>
-    <t>56.6%</t>
-  </si>
-  <si>
-    <t>49.3%</t>
-  </si>
-  <si>
-    <t>27.5%</t>
-  </si>
-  <si>
-    <t>23.4%</t>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>96.8%</t>
+  </si>
+  <si>
+    <t>74.0%</t>
+  </si>
+  <si>
+    <t>50.6%</t>
+  </si>
+  <si>
+    <t>47.9%</t>
+  </si>
+  <si>
+    <t>46.0%</t>
+  </si>
+  <si>
+    <t>28.3%</t>
   </si>
   <si>
     <t>20.9%</t>
   </si>
   <si>
-    <t>17.7%</t>
-  </si>
-  <si>
-    <t>16.8%</t>
-  </si>
-  <si>
-    <t>15.0%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
+    <t>20.7%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-3025</t>
+  </si>
+  <si>
+    <t>-285</t>
+  </si>
+  <si>
+    <t>-102</t>
+  </si>
+  <si>
+    <t>+109</t>
+  </si>
+  <si>
+    <t>+117</t>
+  </si>
+  <si>
+    <t>+253</t>
+  </si>
+  <si>
+    <t>+378</t>
+  </si>
+  <si>
+    <t>+383</t>
+  </si>
+  <si>
+    <t>+635</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>69.3%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
+  </si>
+  <si>
+    <t>4.5%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>1.8%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.3%</t>
   </si>
   <si>
-    <t>-669</t>
-  </si>
-  <si>
-    <t>-517</t>
-  </si>
-  <si>
-    <t>-130</t>
-  </si>
-  <si>
-    <t>+103</t>
-  </si>
-  <si>
-    <t>+264</t>
-  </si>
-  <si>
-    <t>+327</t>
-  </si>
-  <si>
-    <t>+378</t>
-  </si>
-  <si>
-    <t>+465</t>
-  </si>
-  <si>
-    <t>+495</t>
-  </si>
-  <si>
-    <t>+567</t>
-  </si>
-  <si>
-    <t>+5782</t>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>-226</t>
+  </si>
+  <si>
+    <t>+687</t>
+  </si>
+  <si>
+    <t>+2122</t>
+  </si>
+  <si>
+    <t>+2173</t>
+  </si>
+  <si>
+    <t>+2226</t>
+  </si>
+  <si>
+    <t>+5456</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+8233</t>
   </si>
   <si>
     <t>+33233</t>
   </si>
   <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>36.7%</t>
-  </si>
-  <si>
-    <t>35.8%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>8.3%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>1.1%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.9%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>+172</t>
-  </si>
-  <si>
-    <t>+179</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+1105</t>
-  </si>
-  <si>
-    <t>+4445</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+8991</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+11011</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>70.1%</t>
-  </si>
-  <si>
-    <t>15.4%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>2.7%</t>
-  </si>
-  <si>
-    <t>2.6%</t>
-  </si>
-  <si>
-    <t>1.6%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>-234</t>
-  </si>
-  <si>
-    <t>+549</t>
-  </si>
-  <si>
-    <t>+3126</t>
-  </si>
-  <si>
-    <t>+3604</t>
-  </si>
-  <si>
-    <t>+3746</t>
-  </si>
-  <si>
-    <t>+6150</t>
-  </si>
-  <si>
-    <t>+8233</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>85.4%</t>
+  </si>
+  <si>
+    <t>10.7%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>-585</t>
+  </si>
+  <si>
+    <t>+835</t>
+  </si>
+  <si>
+    <t>+2757</t>
   </si>
 </sst>
 </file>
@@ -661,7 +616,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -675,7 +630,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
@@ -703,7 +658,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
@@ -717,7 +672,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
@@ -731,7 +686,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>25</v>
@@ -787,7 +742,7 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
         <v>29</v>
@@ -845,7 +800,7 @@
         <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -853,13 +808,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -867,13 +822,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -887,26 +842,26 @@
         <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
@@ -915,7 +870,7 @@
         <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -923,10 +878,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -934,13 +889,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
@@ -948,13 +903,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>62</v>
@@ -962,16 +917,16 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -979,13 +934,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -996,10 +951,10 @@
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1034,10 +989,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1045,153 +1000,153 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" t="s">
         <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>17</v>
       </c>
       <c r="C4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" t="s">
         <v>68</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
+++ b/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
   <si>
     <t>Record</t>
   </si>
@@ -33,196 +33,205 @@
     <t>Sacks and the City</t>
   </si>
   <si>
+    <t>Hurts Locker Room Talk</t>
+  </si>
+  <si>
+    <t>Tush Push Director 🍑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurts so Good </t>
+  </si>
+  <si>
+    <t>Flock Around and Find Out</t>
+  </si>
+  <si>
+    <t>Rolling with the Homies</t>
+  </si>
+  <si>
+    <t>Immaculate Concepcion</t>
+  </si>
+  <si>
     <t>It's Miller Time</t>
   </si>
   <si>
-    <t>Flock Around and Find Out</t>
-  </si>
-  <si>
-    <t>Tush Push Director 🍑</t>
-  </si>
-  <si>
-    <t>Rolling with the Homies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurts so Good </t>
-  </si>
-  <si>
-    <t>Hurts Locker Room Talk</t>
-  </si>
-  <si>
     <t>Gridiron Grace</t>
   </si>
   <si>
-    <t>Immaculate Concepcion</t>
+    <t>Third Down and Long Story</t>
   </si>
   <si>
     <t>Say Cheese 🧀💚🧀</t>
   </si>
   <si>
-    <t>Third Down and Long Story</t>
-  </si>
-  <si>
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>84.3%</t>
+  </si>
+  <si>
+    <t>75.2%</t>
+  </si>
+  <si>
+    <t>56.4%</t>
+  </si>
+  <si>
+    <t>54.6%</t>
+  </si>
+  <si>
+    <t>40.2%</t>
+  </si>
+  <si>
+    <t>28.9%</t>
+  </si>
+  <si>
+    <t>24.5%</t>
+  </si>
+  <si>
+    <t>23.1%</t>
+  </si>
+  <si>
+    <t>7.0%</t>
+  </si>
+  <si>
+    <t>5.3%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-537</t>
+  </si>
+  <si>
+    <t>-303</t>
+  </si>
+  <si>
+    <t>-129</t>
+  </si>
+  <si>
+    <t>-120</t>
+  </si>
+  <si>
+    <t>+149</t>
+  </si>
+  <si>
+    <t>+246</t>
+  </si>
+  <si>
+    <t>+308</t>
+  </si>
+  <si>
+    <t>+333</t>
+  </si>
+  <si>
+    <t>+1329</t>
+  </si>
+  <si>
+    <t>+1787</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>36.9%</t>
+  </si>
+  <si>
+    <t>24.7%</t>
+  </si>
+  <si>
+    <t>12.8%</t>
+  </si>
+  <si>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>2.3%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>+171</t>
+  </si>
+  <si>
+    <t>+305</t>
+  </si>
+  <si>
+    <t>+681</t>
+  </si>
+  <si>
+    <t>+700</t>
+  </si>
+  <si>
+    <t>+1900</t>
+  </si>
+  <si>
+    <t>+2603</t>
+  </si>
+  <si>
+    <t>+4248</t>
+  </si>
+  <si>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>+49900</t>
   </si>
   <si>
     <t>96.8%</t>
   </si>
   <si>
-    <t>74.0%</t>
-  </si>
-  <si>
-    <t>50.6%</t>
-  </si>
-  <si>
-    <t>47.9%</t>
-  </si>
-  <si>
-    <t>46.0%</t>
-  </si>
-  <si>
-    <t>28.3%</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>20.7%</t>
-  </si>
-  <si>
-    <t>13.6%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
+    <t>2.2%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>-3025</t>
   </si>
   <si>
-    <t>-285</t>
-  </si>
-  <si>
-    <t>-102</t>
-  </si>
-  <si>
-    <t>+109</t>
-  </si>
-  <si>
-    <t>+117</t>
-  </si>
-  <si>
-    <t>+253</t>
-  </si>
-  <si>
-    <t>+378</t>
-  </si>
-  <si>
-    <t>+383</t>
-  </si>
-  <si>
-    <t>+635</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>69.3%</t>
-  </si>
-  <si>
-    <t>12.7%</t>
-  </si>
-  <si>
-    <t>4.5%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>4.3%</t>
-  </si>
-  <si>
-    <t>1.8%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-226</t>
-  </si>
-  <si>
-    <t>+687</t>
-  </si>
-  <si>
-    <t>+2122</t>
-  </si>
-  <si>
-    <t>+2173</t>
-  </si>
-  <si>
-    <t>+2226</t>
-  </si>
-  <si>
-    <t>+5456</t>
-  </si>
-  <si>
-    <t>+7043</t>
-  </si>
-  <si>
-    <t>+8233</t>
+    <t>+4445</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+33233</t>
-  </si>
-  <si>
-    <t>85.4%</t>
-  </si>
-  <si>
-    <t>10.7%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>-585</t>
-  </si>
-  <si>
-    <t>+835</t>
-  </si>
-  <si>
-    <t>+2757</t>
   </si>
 </sst>
 </file>
@@ -605,10 +614,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -616,13 +625,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -630,13 +639,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -644,13 +653,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -658,13 +667,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -675,10 +684,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -689,10 +698,10 @@
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -700,13 +709,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -714,13 +723,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -728,13 +737,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -742,13 +751,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -756,13 +765,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +792,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -797,7 +806,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -808,10 +817,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
         <v>55</v>
@@ -819,13 +828,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -833,13 +842,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -850,10 +859,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
         <v>58</v>
@@ -861,13 +870,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
         <v>59</v>
@@ -875,13 +884,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>60</v>
@@ -889,13 +898,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>61</v>
@@ -903,13 +912,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
         <v>62</v>
@@ -917,16 +926,16 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -934,13 +943,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -948,13 +957,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +984,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -986,13 +995,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1000,13 +1009,13 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1014,13 +1023,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1028,55 +1037,55 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1087,66 +1096,66 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
+++ b/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
   <si>
     <t>Record</t>
   </si>
@@ -36,202 +36,193 @@
     <t>Hurts Locker Room Talk</t>
   </si>
   <si>
+    <t>It's Miller Time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurts so Good </t>
+  </si>
+  <si>
+    <t>Flock Around and Find Out</t>
+  </si>
+  <si>
+    <t>Rolling with the Homies</t>
+  </si>
+  <si>
+    <t>Gridiron Grace</t>
+  </si>
+  <si>
     <t>Tush Push Director 🍑</t>
   </si>
   <si>
-    <t xml:space="preserve">Hurts so Good </t>
-  </si>
-  <si>
-    <t>Flock Around and Find Out</t>
-  </si>
-  <si>
-    <t>Rolling with the Homies</t>
+    <t>Third Down and Long Story</t>
   </si>
   <si>
     <t>Immaculate Concepcion</t>
   </si>
   <si>
-    <t>It's Miller Time</t>
-  </si>
-  <si>
-    <t>Gridiron Grace</t>
-  </si>
-  <si>
-    <t>Third Down and Long Story</t>
-  </si>
-  <si>
     <t>Say Cheese 🧀💚🧀</t>
   </si>
   <si>
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>84.3%</t>
-  </si>
-  <si>
-    <t>75.2%</t>
-  </si>
-  <si>
-    <t>56.4%</t>
-  </si>
-  <si>
-    <t>54.6%</t>
-  </si>
-  <si>
-    <t>40.2%</t>
-  </si>
-  <si>
-    <t>28.9%</t>
-  </si>
-  <si>
-    <t>24.5%</t>
-  </si>
-  <si>
-    <t>23.1%</t>
-  </si>
-  <si>
-    <t>7.0%</t>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>84.6%</t>
+  </si>
+  <si>
+    <t>78.4%</t>
+  </si>
+  <si>
+    <t>62.8%</t>
+  </si>
+  <si>
+    <t>43.0%</t>
+  </si>
+  <si>
+    <t>41.5%</t>
+  </si>
+  <si>
+    <t>38.2%</t>
+  </si>
+  <si>
+    <t>26.9%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
+  </si>
+  <si>
+    <t>5.8%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-549</t>
+  </si>
+  <si>
+    <t>-363</t>
+  </si>
+  <si>
+    <t>-169</t>
+  </si>
+  <si>
+    <t>+133</t>
+  </si>
+  <si>
+    <t>+141</t>
+  </si>
+  <si>
+    <t>+162</t>
+  </si>
+  <si>
+    <t>+272</t>
+  </si>
+  <si>
+    <t>+533</t>
+  </si>
+  <si>
+    <t>+1624</t>
+  </si>
+  <si>
+    <t>+3348</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>38.7%</t>
+  </si>
+  <si>
+    <t>26.5%</t>
+  </si>
+  <si>
+    <t>12.5%</t>
+  </si>
+  <si>
+    <t>6.3%</t>
+  </si>
+  <si>
+    <t>6.1%</t>
   </si>
   <si>
     <t>5.3%</t>
   </si>
   <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-537</t>
-  </si>
-  <si>
-    <t>-303</t>
-  </si>
-  <si>
-    <t>-129</t>
-  </si>
-  <si>
-    <t>-120</t>
-  </si>
-  <si>
-    <t>+149</t>
-  </si>
-  <si>
-    <t>+246</t>
-  </si>
-  <si>
-    <t>+308</t>
-  </si>
-  <si>
-    <t>+333</t>
-  </si>
-  <si>
-    <t>+1329</t>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>+158</t>
+  </si>
+  <si>
+    <t>+277</t>
+  </si>
+  <si>
+    <t>+700</t>
+  </si>
+  <si>
+    <t>+1487</t>
+  </si>
+  <si>
+    <t>+1539</t>
   </si>
   <si>
     <t>+1787</t>
   </si>
   <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>+5782</t>
+  </si>
+  <si>
     <t>+19900</t>
   </si>
   <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>36.9%</t>
-  </si>
-  <si>
-    <t>24.7%</t>
-  </si>
-  <si>
-    <t>12.8%</t>
-  </si>
-  <si>
-    <t>12.5%</t>
-  </si>
-  <si>
-    <t>5.0%</t>
-  </si>
-  <si>
-    <t>3.7%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>+171</t>
-  </si>
-  <si>
-    <t>+305</t>
-  </si>
-  <si>
-    <t>+681</t>
-  </si>
-  <si>
-    <t>+700</t>
-  </si>
-  <si>
-    <t>+1900</t>
-  </si>
-  <si>
-    <t>+2603</t>
-  </si>
-  <si>
-    <t>+4248</t>
-  </si>
-  <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>96.8%</t>
-  </si>
-  <si>
-    <t>2.2%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-3025</t>
-  </si>
-  <si>
-    <t>+4445</t>
-  </si>
-  <si>
-    <t>+24900</t>
-  </si>
-  <si>
     <t>+33233</t>
+  </si>
+  <si>
+    <t>95.9%</t>
+  </si>
+  <si>
+    <t>3.5%</t>
+  </si>
+  <si>
+    <t>-2339</t>
+  </si>
+  <si>
+    <t>+2757</t>
   </si>
 </sst>
 </file>
@@ -614,10 +605,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -625,13 +616,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -639,13 +630,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -656,10 +647,10 @@
         <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -667,13 +658,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -684,10 +675,10 @@
         <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -695,13 +686,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -712,10 +703,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -723,13 +714,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -737,13 +728,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -751,13 +742,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -765,10 +756,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
         <v>43</v>
@@ -809,7 +800,7 @@
         <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -817,32 +808,32 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>17</v>
@@ -851,26 +842,26 @@
         <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
         <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -879,7 +870,7 @@
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -887,13 +878,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -907,12 +898,12 @@
         <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>16</v>
@@ -921,21 +912,21 @@
         <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -943,10 +934,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -957,10 +948,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
         <v>43</v>
@@ -995,13 +986,13 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1009,66 +1000,66 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>43</v>
@@ -1076,13 +1067,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
         <v>43</v>
@@ -1090,13 +1081,13 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
@@ -1104,13 +1095,13 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
         <v>43</v>
@@ -1118,13 +1109,13 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
         <v>43</v>
@@ -1132,13 +1123,13 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -1146,13 +1137,13 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D13" t="s">
         <v>43</v>

--- a/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
+++ b/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
@@ -30,33 +30,33 @@
     <t>Team</t>
   </si>
   <si>
+    <t>RIP Jalen 😭</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hurts so Good </t>
+  </si>
+  <si>
     <t>Sacks and the City</t>
   </si>
   <si>
-    <t>Hurts Locker Room Talk</t>
+    <t>Rolling with the Homies</t>
+  </si>
+  <si>
+    <t>Gridiron Grace</t>
+  </si>
+  <si>
+    <t>Flock Around and Find Out</t>
   </si>
   <si>
     <t>It's Miller Time</t>
   </si>
   <si>
-    <t xml:space="preserve">Hurts so Good </t>
-  </si>
-  <si>
-    <t>Flock Around and Find Out</t>
-  </si>
-  <si>
-    <t>Rolling with the Homies</t>
-  </si>
-  <si>
-    <t>Gridiron Grace</t>
+    <t>Third Down and Long Story</t>
   </si>
   <si>
     <t>Tush Push Director 🍑</t>
   </si>
   <si>
-    <t>Third Down and Long Story</t>
-  </si>
-  <si>
     <t>Immaculate Concepcion</t>
   </si>
   <si>
@@ -66,163 +66,163 @@
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>84.6%</t>
-  </si>
-  <si>
-    <t>78.4%</t>
-  </si>
-  <si>
-    <t>62.8%</t>
-  </si>
-  <si>
-    <t>43.0%</t>
-  </si>
-  <si>
-    <t>41.5%</t>
-  </si>
-  <si>
-    <t>38.2%</t>
-  </si>
-  <si>
-    <t>26.9%</t>
-  </si>
-  <si>
-    <t>15.8%</t>
-  </si>
-  <si>
-    <t>5.8%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>0-6</t>
+  </si>
+  <si>
+    <t>88.0%</t>
+  </si>
+  <si>
+    <t>67.8%</t>
+  </si>
+  <si>
+    <t>58.5%</t>
+  </si>
+  <si>
+    <t>48.9%</t>
+  </si>
+  <si>
+    <t>42.4%</t>
+  </si>
+  <si>
+    <t>35.6%</t>
+  </si>
+  <si>
+    <t>31.5%</t>
+  </si>
+  <si>
+    <t>15.6%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
+  </si>
+  <si>
+    <t>1.2%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-733</t>
+  </si>
+  <si>
+    <t>-211</t>
+  </si>
+  <si>
+    <t>-141</t>
+  </si>
+  <si>
+    <t>+104</t>
+  </si>
+  <si>
+    <t>+136</t>
+  </si>
+  <si>
+    <t>+181</t>
+  </si>
+  <si>
+    <t>+217</t>
+  </si>
+  <si>
+    <t>+541</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>+4900</t>
+  </si>
+  <si>
+    <t>+8233</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>43.8%</t>
+  </si>
+  <si>
+    <t>20.3%</t>
+  </si>
+  <si>
+    <t>12.7%</t>
+  </si>
+  <si>
+    <t>8.9%</t>
+  </si>
+  <si>
+    <t>6.3%</t>
+  </si>
+  <si>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-549</t>
-  </si>
-  <si>
-    <t>-363</t>
-  </si>
-  <si>
-    <t>-169</t>
-  </si>
-  <si>
-    <t>+133</t>
-  </si>
-  <si>
-    <t>+141</t>
-  </si>
-  <si>
-    <t>+162</t>
-  </si>
-  <si>
-    <t>+272</t>
-  </si>
-  <si>
-    <t>+533</t>
-  </si>
-  <si>
-    <t>+1624</t>
-  </si>
-  <si>
-    <t>+3348</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>38.7%</t>
-  </si>
-  <si>
-    <t>26.5%</t>
-  </si>
-  <si>
-    <t>12.5%</t>
-  </si>
-  <si>
-    <t>6.3%</t>
-  </si>
-  <si>
-    <t>6.1%</t>
-  </si>
-  <si>
-    <t>5.3%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>+158</t>
-  </si>
-  <si>
-    <t>+277</t>
-  </si>
-  <si>
-    <t>+700</t>
+    <t>+128</t>
+  </si>
+  <si>
+    <t>+393</t>
+  </si>
+  <si>
+    <t>+687</t>
+  </si>
+  <si>
+    <t>+1024</t>
   </si>
   <si>
     <t>+1487</t>
   </si>
   <si>
-    <t>+1539</t>
-  </si>
-  <si>
-    <t>+1787</t>
-  </si>
-  <si>
-    <t>+4662</t>
-  </si>
-  <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>95.9%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>-2339</t>
-  </si>
-  <si>
-    <t>+2757</t>
+    <t>+2841</t>
+  </si>
+  <si>
+    <t>+4067</t>
+  </si>
+  <si>
+    <t>+7592</t>
+  </si>
+  <si>
+    <t>+16567</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>99.7%</t>
+  </si>
+  <si>
+    <t>-33233</t>
   </si>
 </sst>
 </file>
@@ -616,7 +616,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -630,7 +630,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -644,7 +644,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>24</v>
@@ -658,7 +658,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -672,7 +672,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -714,7 +714,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
@@ -728,7 +728,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -762,7 +762,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +783,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -797,10 +797,10 @@
         <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -808,13 +808,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -822,13 +822,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -836,55 +836,55 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -895,10 +895,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -906,13 +906,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -920,13 +920,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -937,10 +937,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -954,7 +954,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -989,10 +989,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1003,38 +1003,38 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" t="s">
         <v>66</v>
-      </c>
-      <c r="D3" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1048,12 +1048,12 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
@@ -1062,26 +1062,26 @@
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>16</v>
@@ -1090,40 +1090,40 @@
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1132,12 +1132,12 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -1146,7 +1146,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
+++ b/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
   <si>
     <t>Record</t>
   </si>
@@ -30,124 +30,121 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Sacks and the City</t>
+  </si>
+  <si>
+    <t>Rolling with the Homies</t>
+  </si>
+  <si>
     <t>RIP Jalen 😭</t>
   </si>
   <si>
+    <t>Flock Around and Find Out</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hurts so Good </t>
   </si>
   <si>
-    <t>Sacks and the City</t>
-  </si>
-  <si>
-    <t>Rolling with the Homies</t>
+    <t>It's Miller Time</t>
   </si>
   <si>
     <t>Gridiron Grace</t>
   </si>
   <si>
-    <t>Flock Around and Find Out</t>
-  </si>
-  <si>
-    <t>It's Miller Time</t>
+    <t>Tush Push Director 🍑</t>
   </si>
   <si>
     <t>Third Down and Long Story</t>
   </si>
   <si>
-    <t>Tush Push Director 🍑</t>
+    <t>Say Cheese 🧀💚🧀</t>
   </si>
   <si>
     <t>Immaculate Concepcion</t>
   </si>
   <si>
-    <t>Say Cheese 🧀💚🧀</t>
-  </si>
-  <si>
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>88.0%</t>
-  </si>
-  <si>
-    <t>67.8%</t>
-  </si>
-  <si>
-    <t>58.5%</t>
-  </si>
-  <si>
-    <t>48.9%</t>
-  </si>
-  <si>
-    <t>42.4%</t>
-  </si>
-  <si>
-    <t>35.6%</t>
-  </si>
-  <si>
-    <t>31.5%</t>
-  </si>
-  <si>
-    <t>15.6%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
-  </si>
-  <si>
-    <t>1.2%</t>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>2-5</t>
+  </si>
+  <si>
+    <t>0-7</t>
+  </si>
+  <si>
+    <t>78.4%</t>
+  </si>
+  <si>
+    <t>77.3%</t>
+  </si>
+  <si>
+    <t>71.6%</t>
+  </si>
+  <si>
+    <t>50.0%</t>
+  </si>
+  <si>
+    <t>48.3%</t>
+  </si>
+  <si>
+    <t>39.7%</t>
+  </si>
+  <si>
+    <t>21.3%</t>
+  </si>
+  <si>
+    <t>5.6%</t>
+  </si>
+  <si>
+    <t>4.4%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-733</t>
-  </si>
-  <si>
-    <t>-211</t>
-  </si>
-  <si>
-    <t>-141</t>
-  </si>
-  <si>
-    <t>+104</t>
-  </si>
-  <si>
-    <t>+136</t>
-  </si>
-  <si>
-    <t>+181</t>
-  </si>
-  <si>
-    <t>+217</t>
-  </si>
-  <si>
-    <t>+541</t>
-  </si>
-  <si>
-    <t>+1076</t>
-  </si>
-  <si>
-    <t>+4900</t>
-  </si>
-  <si>
-    <t>+8233</t>
+    <t>-363</t>
+  </si>
+  <si>
+    <t>-341</t>
+  </si>
+  <si>
+    <t>-252</t>
+  </si>
+  <si>
+    <t>-100</t>
+  </si>
+  <si>
+    <t>+107</t>
+  </si>
+  <si>
+    <t>+152</t>
+  </si>
+  <si>
+    <t>+369</t>
+  </si>
+  <si>
+    <t>+1686</t>
+  </si>
+  <si>
+    <t>+2173</t>
+  </si>
+  <si>
+    <t>+2930</t>
   </si>
   <si>
     <t>+99900</t>
@@ -156,73 +153,70 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>43.8%</t>
-  </si>
-  <si>
-    <t>20.3%</t>
-  </si>
-  <si>
-    <t>12.7%</t>
-  </si>
-  <si>
-    <t>8.9%</t>
-  </si>
-  <si>
-    <t>6.3%</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>28.4%</t>
+  </si>
+  <si>
+    <t>28.2%</t>
+  </si>
+  <si>
+    <t>19.8%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
+  </si>
+  <si>
+    <t>6.1%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>+128</t>
-  </si>
-  <si>
-    <t>+393</t>
-  </si>
-  <si>
-    <t>+687</t>
-  </si>
-  <si>
-    <t>+1024</t>
-  </si>
-  <si>
-    <t>+1487</t>
-  </si>
-  <si>
-    <t>+2841</t>
-  </si>
-  <si>
-    <t>+4067</t>
-  </si>
-  <si>
-    <t>+7592</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>+252</t>
+  </si>
+  <si>
+    <t>+255</t>
+  </si>
+  <si>
+    <t>+405</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>+1393</t>
+  </si>
+  <si>
+    <t>+1539</t>
+  </si>
+  <si>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>+49900</t>
   </si>
   <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>-33233</t>
+    <t>99.6%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>-24900</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
 </sst>
 </file>
@@ -630,7 +624,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -658,7 +652,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -672,7 +666,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -714,7 +708,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
@@ -728,7 +722,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
         <v>30</v>
@@ -762,7 +756,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -783,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -791,30 +785,30 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -822,69 +816,69 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -895,10 +889,10 @@
         <v>16</v>
       </c>
       <c r="C9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -906,13 +900,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -920,13 +914,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -937,10 +931,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -954,7 +948,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -975,7 +969,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -989,10 +983,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1003,7 +997,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
         <v>66</v>
@@ -1011,16 +1005,16 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1028,41 +1022,41 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1070,60 +1064,60 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
@@ -1132,21 +1126,21 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
+++ b/data/odds/The Girl's Room 💞🏈 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="64">
   <si>
     <t>Record</t>
   </si>
@@ -30,21 +30,21 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Rolling with the Homies</t>
+  </si>
+  <si>
     <t>Sacks and the City</t>
   </si>
   <si>
-    <t>Rolling with the Homies</t>
-  </si>
-  <si>
     <t>RIP Jalen 😭</t>
   </si>
   <si>
+    <t xml:space="preserve">Hurts so Good </t>
+  </si>
+  <si>
     <t>Flock Around and Find Out</t>
   </si>
   <si>
-    <t xml:space="preserve">Hurts so Good </t>
-  </si>
-  <si>
     <t>It's Miller Time</t>
   </si>
   <si>
@@ -66,12 +66,12 @@
     <t xml:space="preserve">michelle’s boy toys </t>
   </si>
   <si>
+    <t>5-2</t>
+  </si>
+  <si>
     <t>4-3</t>
   </si>
   <si>
-    <t>5-2</t>
-  </si>
-  <si>
     <t>3-4</t>
   </si>
   <si>
@@ -81,70 +81,73 @@
     <t>0-7</t>
   </si>
   <si>
-    <t>78.4%</t>
-  </si>
-  <si>
-    <t>77.3%</t>
-  </si>
-  <si>
-    <t>71.6%</t>
-  </si>
-  <si>
-    <t>50.0%</t>
-  </si>
-  <si>
-    <t>48.3%</t>
-  </si>
-  <si>
-    <t>39.7%</t>
-  </si>
-  <si>
-    <t>21.3%</t>
-  </si>
-  <si>
-    <t>5.6%</t>
-  </si>
-  <si>
-    <t>4.4%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>76.4%</t>
+  </si>
+  <si>
+    <t>73.0%</t>
+  </si>
+  <si>
+    <t>47.1%</t>
+  </si>
+  <si>
+    <t>46.4%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>22.3%</t>
+  </si>
+  <si>
+    <t>7.6%</t>
+  </si>
+  <si>
+    <t>3.7%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-363</t>
-  </si>
-  <si>
-    <t>-341</t>
-  </si>
-  <si>
-    <t>-252</t>
-  </si>
-  <si>
-    <t>-100</t>
-  </si>
-  <si>
-    <t>+107</t>
-  </si>
-  <si>
-    <t>+152</t>
-  </si>
-  <si>
-    <t>+369</t>
-  </si>
-  <si>
-    <t>+1686</t>
-  </si>
-  <si>
-    <t>+2173</t>
-  </si>
-  <si>
-    <t>+2930</t>
+    <t>-400</t>
+  </si>
+  <si>
+    <t>-324</t>
+  </si>
+  <si>
+    <t>-270</t>
+  </si>
+  <si>
+    <t>+112</t>
+  </si>
+  <si>
+    <t>+116</t>
+  </si>
+  <si>
+    <t>+150</t>
+  </si>
+  <si>
+    <t>+348</t>
+  </si>
+  <si>
+    <t>+1216</t>
+  </si>
+  <si>
+    <t>+2603</t>
+  </si>
+  <si>
+    <t>+3025</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
   <si>
     <t>+99900</t>
@@ -153,55 +156,49 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>28.4%</t>
-  </si>
-  <si>
-    <t>28.2%</t>
-  </si>
-  <si>
-    <t>19.8%</t>
-  </si>
-  <si>
-    <t>8.6%</t>
-  </si>
-  <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>6.1%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
+    <t>30.9%</t>
+  </si>
+  <si>
+    <t>25.1%</t>
+  </si>
+  <si>
+    <t>19.9%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
   </si>
   <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>+252</t>
-  </si>
-  <si>
-    <t>+255</t>
-  </si>
-  <si>
-    <t>+405</t>
-  </si>
-  <si>
-    <t>+1063</t>
-  </si>
-  <si>
-    <t>+1393</t>
-  </si>
-  <si>
-    <t>+1539</t>
-  </si>
-  <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>+224</t>
+  </si>
+  <si>
+    <t>+298</t>
+  </si>
+  <si>
+    <t>+403</t>
+  </si>
+  <si>
+    <t>+1182</t>
+  </si>
+  <si>
+    <t>+1438</t>
+  </si>
+  <si>
+    <t>+3604</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
   <si>
     <t>+49900</t>
@@ -210,13 +207,7 @@
     <t>99.6%</t>
   </si>
   <si>
-    <t>0.4%</t>
-  </si>
-  <si>
     <t>-24900</t>
-  </si>
-  <si>
-    <t>+24900</t>
   </si>
 </sst>
 </file>
@@ -624,7 +615,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>23</v>
@@ -666,7 +657,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
@@ -694,7 +685,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>28</v>
@@ -708,7 +699,7 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>29</v>
@@ -756,7 +747,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -777,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -785,13 +776,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D2" t="s">
         <v>54</v>
@@ -799,13 +790,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
         <v>55</v>
@@ -816,10 +807,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
         <v>56</v>
@@ -827,13 +818,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
         <v>57</v>
@@ -841,13 +832,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>58</v>
@@ -855,16 +846,16 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>50</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -878,7 +869,7 @@
         <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -886,13 +877,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
         <v>52</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -900,13 +891,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -920,7 +911,7 @@
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -934,7 +925,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -948,7 +939,7 @@
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -969,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -983,10 +974,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" t="s">
         <v>63</v>
-      </c>
-      <c r="D2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -997,10 +988,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1008,13 +999,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1022,13 +1013,13 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1042,21 +1033,21 @@
         <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1064,13 +1055,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1084,7 +1075,7 @@
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1092,55 +1083,55 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
